--- a/artfynd/A 14565-2025 artfynd.xlsx
+++ b/artfynd/A 14565-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73380066</v>
+        <v>89595582</v>
       </c>
       <c r="B2" t="n">
-        <v>90634</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,47 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6055</v>
+        <v>149</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ö om korsning Råndalsvägen -- Kvarnån, Kvarnån, Hede, Hjd</t>
+          <t>Norr om Kvarnån, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422001.8124013628</v>
+        <v>421948</v>
       </c>
       <c r="R2" t="n">
-        <v>6917626.829723534</v>
+        <v>6917641</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-09-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-09-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,34 +754,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>J-M Roberge</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>84081459</v>
+        <v>119703032</v>
       </c>
       <c r="B3" t="n">
-        <v>90634</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,40 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6055</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Enarsängsvägen, Hjd</t>
+          <t>Enarsängsvägen, Enarsängsvägen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422017.2139774631</v>
+        <v>422001</v>
       </c>
       <c r="R3" t="n">
-        <v>6917529.935642023</v>
+        <v>6917511</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +841,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-09-21</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-09-21</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +865,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -914,15 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89595581</v>
+        <v>119703004</v>
       </c>
       <c r="B4" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,37 +894,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norr om Kvarnån, Hjd</t>
+          <t>Enarsängsvägen, Enarsängsvägen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>421963.1301685566</v>
+        <v>422002</v>
       </c>
       <c r="R4" t="n">
-        <v>6917682.031992282</v>
+        <v>6917483</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,22 +948,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-09-28</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-09-28</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,53 +978,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89595582</v>
+        <v>89595581</v>
       </c>
       <c r="B5" t="n">
-        <v>90641</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>421948.2309975958</v>
+        <v>421963</v>
       </c>
       <c r="R5" t="n">
-        <v>6917641.07500002</v>
+        <v>6917682</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,19 +1058,9 @@
           <t>2020-09-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,12 +1094,7 @@
         <v>119702988</v>
       </c>
       <c r="B6" t="n">
-        <v>91844</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,15 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119702916</v>
+        <v>119703023</v>
       </c>
       <c r="B7" t="n">
-        <v>89252</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,21 +1209,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6276</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1298,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>421952</v>
+        <v>421996</v>
       </c>
       <c r="R7" t="n">
-        <v>6917505</v>
+        <v>6917498</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1370,37 +1305,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119703032</v>
+        <v>119703185</v>
       </c>
       <c r="B8" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2059</v>
+        <v>4365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1410,10 +1340,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>422001</v>
+        <v>422022</v>
       </c>
       <c r="R8" t="n">
-        <v>6917511</v>
+        <v>6917669</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1445,7 +1375,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1385,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,15 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119703004</v>
+        <v>119703246</v>
       </c>
       <c r="B9" t="n">
-        <v>91826</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90522</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3100</v>
+        <v>4962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>422002</v>
+        <v>421950</v>
       </c>
       <c r="R9" t="n">
-        <v>6917483</v>
+        <v>6917559</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1557,7 +1482,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1492,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,15 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119703023</v>
+        <v>119702916</v>
       </c>
       <c r="B10" t="n">
-        <v>91844</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,21 +1530,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4365</v>
+        <v>6276</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1634,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>421996</v>
+        <v>421952</v>
       </c>
       <c r="R10" t="n">
-        <v>6917498</v>
+        <v>6917505</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1703,230 +1623,6 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>119703015</v>
-      </c>
-      <c r="B11" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Enarsängsvägen, Enarsängsvägen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>421996</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6917498</v>
-      </c>
-      <c r="S11" t="n">
-        <v>25</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Hede</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Andreas Öster</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Andreas Öster</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>119703185</v>
-      </c>
-      <c r="B12" t="n">
-        <v>91862</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>4365</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Smalfotad taggsvamp</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Hydnellum gracilipes</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Enarsängsvägen, Enarsängsvägen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>422022</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6917669</v>
-      </c>
-      <c r="S12" t="n">
-        <v>25</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Hede</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Andreas Öster</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Andreas Öster</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14565-2025 artfynd.xlsx
+++ b/artfynd/A 14565-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595582</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119703032</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119703004</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595581</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119702988</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119703023</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,6 +1444,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119703185</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1516,6 +1556,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119703246</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1623,8 +1668,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119702916</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>